--- a/Result/profitability/3312.xlsx
+++ b/Result/profitability/3312.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4125</v>
+        <v>0.4762499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>5.09125</v>
+        <v>5.070000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3149999999999999</v>
+        <v>0.32375</v>
       </c>
       <c r="N3" t="n">
-        <v>4.908750000000001</v>
+        <v>4.915</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>0.32</v>
+        <v>0.29125</v>
       </c>
       <c r="N4" t="n">
-        <v>4.825</v>
+        <v>4.696250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1675</v>
+        <v>0.46</v>
       </c>
       <c r="N5" t="n">
-        <v>4.393750000000001</v>
+        <v>4.47875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.76</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4525</v>
+        <v>0.4249999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>4.565</v>
+        <v>4.616250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4025</v>
+        <v>0.3575</v>
       </c>
       <c r="N7" t="n">
-        <v>4.796250000000001</v>
+        <v>4.74</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3375</v>
+        <v>0.31125</v>
       </c>
       <c r="N8" t="n">
-        <v>4.72625</v>
+        <v>4.705000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.43</v>
       </c>
       <c r="N10" t="n">
-        <v>4.880000000000001</v>
+        <v>4.88</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0.55</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>5.03125</v>
@@ -2026,7 +2026,7 @@
         <v>-0.11</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4937499999999999</v>
+        <v>0.49375</v>
       </c>
       <c r="N13" t="n">
         <v>4.9</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6556</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6218</v>
+      </c>
+      <c r="E75" t="n">
+        <v>338</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>183</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>170</v>
+      </c>
+      <c r="K75" t="n">
+        <v>149</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.245000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2038834951456311</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03189493433395874</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.539473684210526</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.6799999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1517857142857142</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
